--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.108.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.108.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.108.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.108.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: å­¦</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+5B66 CJK UNIFIED IDEOGRAPH-5B66 | isolated marker/symbol line :: 学</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ï»¿â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]—</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]—</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L36: isolated marker/symbol line :: 101</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 101</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]—</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -624,7 +628,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the Mas-</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -645,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -657,19 +665,19 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the Mas-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: å­¦</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+5B66 CJK UNIFIED IDEOGRAPH-5B66 | isolated marker/symbol line :: 学</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 1</t>
+          <t>L58: isolated marker/symbol line :: 101</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -706,11 +714,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ the Mas-</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -720,7 +724,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: *</t>
+          <t>L96: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -747,7 +751,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -767,7 +771,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: A</t>
+          <t>L107: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -812,7 +816,11 @@
           <t>L135: isolated marker/symbol line :: D</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L114: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -966,7 +974,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1005,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1044,7 +1052,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1122,7 +1130,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
